--- a/artfynd/S 667-2021 artfynd.xlsx
+++ b/artfynd/S 667-2021 artfynd.xlsx
@@ -15933,7 +15933,7 @@
         <v>104191000</v>
       </c>
       <c r="B132" t="n">
-        <v>89235</v>
+        <v>89237</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/S 667-2021 artfynd.xlsx
+++ b/artfynd/S 667-2021 artfynd.xlsx
@@ -15933,7 +15933,7 @@
         <v>104191000</v>
       </c>
       <c r="B132" t="n">
-        <v>89237</v>
+        <v>89239</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>

--- a/artfynd/S 667-2021 artfynd.xlsx
+++ b/artfynd/S 667-2021 artfynd.xlsx
@@ -15933,7 +15933,7 @@
         <v>104191000</v>
       </c>
       <c r="B132" t="n">
-        <v>89239</v>
+        <v>89241</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
